--- a/InputData/indst/_cement/CKFSR/Cement Kiln Fuel Shift Recipient Fractions.xlsx
+++ b/InputData/indst/_cement/CKFSR/Cement Kiln Fuel Shift Recipient Fractions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CKFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181519D2-31EE-49B5-98B9-B323E4BEA1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289B923F-A657-4032-A755-C2461ECA3618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31095" yWindow="2295" windowWidth="21600" windowHeight="12585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
   <si>
     <t>CKFSR Cement Kiln Fuel Shift Recipient Fractions</t>
   </si>
@@ -80,19 +80,19 @@
     <t>Purpose and layout</t>
   </si>
   <si>
-    <t>The kiln fuel shift policy (Fraction of Fossil Kiln Energy Shifted) takes the same share of every fossil fuel the kilns burn: coal, natural gas, and the petroleum coke the model carries on the petroleum diesel and residual fuel oil elements. This file says where that shifted energy goes. Each fossil fuel's row splits its shifted energy across three destinations: alternative fuels (tire-derived fuel, engineered waste fuels, waste oils and solvents, biomass residues, which the model carries on the biomass element), natural gas, and hydrogen. Each fossil row must add up to one. Rows for the other fuels are not used and stay zero. Edit the 'Recipient Fractions' tab; the 'Checks' tab tests the rows; the 'CKFSR' tab is exported to CKFSR.csv.</t>
+    <t>The kiln fuel shift policy (Fraction of Fossil Kiln Energy Shifted) takes the same share of every fossil fuel the kilns burn: coal, natural gas, and the petroleum coke the model carries on the petroleum diesel and residual fuel oil elements. This file says which fuel replaces it, in the same layout as the model's other source-to-target tables (hydrogen pathway shifting, BRHPF; feedstock shifting, IFSRF): each column is a fuel the kilns stop burning, each row is a fuel that replaces it. Alternative fuels (tire-derived fuel, engineered waste fuels, waste oils and solvents, biomass residues) are carried on the biomass row and priced at the biomass price. Each fossil column must add up to one; columns for the other fuels are not used and stay zero. Edit the 'Recipient Fractions' tab; the 'Checks' tab tests the columns; the 'CKFSR' tab is exported to CKFSR.csv.</t>
   </si>
   <si>
     <t>How the U.S. values were set</t>
   </si>
   <si>
-    <t>For the U.S. every fossil kiln fuel sends all of its shifted energy to alternative fuels, because nearly all kiln-fuel policy in force or proposed is a thermal substitution target. With these values the policy setting is simply the share of fossil kiln heat replaced by alternative fuels. A target T for a fleet that already gets a share A of its kiln heat from alternative fuels corresponds to a setting of (T - A) / (1 - A).</t>
-  </si>
-  <si>
-    <t>Other ways to use the rows</t>
-  </si>
-  <si>
-    <t>A coal-to-gas kiln conversion program, as in parts of China, sends the coal and petroleum coke rows to natural gas and leaves the natural gas row on natural gas (a fuel sent to itself is unchanged). A hydrogen co-firing program sends every fossil row to hydrogen. A mixed policy splits a row, for example half of coal to alternative fuels and half to natural gas. The same policy setting then applies to whatever routing the rows describe.</t>
+    <t>For the U.S. every fossil kiln fuel sends all of its shifted energy to biomass (alternative fuels), because nearly all kiln-fuel policy in force or proposed is a thermal substitution target. With these values the policy setting is simply the share of fossil kiln heat replaced by alternative fuels. A target T for a fleet that already gets a share A of its kiln heat from alternative fuels corresponds to a setting of (T - A) / (1 - A).</t>
+  </si>
+  <si>
+    <t>Other ways to use the columns</t>
+  </si>
+  <si>
+    <t>A coal-to-gas kiln conversion program, as in parts of China, sends the coal and petroleum coke columns to the natural gas row and leaves the natural gas column on natural gas (a fuel sent to itself is unchanged). A hydrogen co-firing program sends every fossil column to a hydrogen row. A mixed policy splits a column, for example half of coal to biomass and half to natural gas. The same policy setting then applies to whatever routing the columns describe.</t>
   </si>
   <si>
     <t>Confidence</t>
@@ -101,110 +101,144 @@
     <t>The U.S. routing is a modelling choice that matches how kiln-fuel policies are written, not a measured quantity. Kilns fire coarse solid wastes mainly in place of coal and petroleum coke, so a uniform share across the fuels may take somewhat more from natural gas than real plants would.</t>
   </si>
   <si>
-    <t>Where each fossil kiln fuel's shifted energy goes (edit here)</t>
-  </si>
-  <si>
-    <t>Each row is one fuel in the model's fuel list. For the four fossil kiln fuels, enter the fraction of the energy the policy takes from that fuel that goes to each destination; the three fractions must add up to one. Leave the other rows at zero.</t>
-  </si>
-  <si>
-    <t>Fuel</t>
+    <t>Which fuel replaces each fossil kiln fuel (edit here)</t>
+  </si>
+  <si>
+    <t>Each column is a fuel the kilns stop burning; each row is a fuel that replaces it. For the four fossil kiln fuels (marked 1 in row 4), enter the fraction of the shifted energy that goes to each replacing fuel; each of those columns must add up to one. Leave the other columns at zero.</t>
+  </si>
+  <si>
+    <t>To fuel (below) / From fuel (right)</t>
   </si>
   <si>
     <t>Model fuel name</t>
   </si>
   <si>
-    <t>Fossil kiln fuel?
-1 = yes</t>
-  </si>
-  <si>
-    <t>To alternative fuels
-fraction</t>
-  </si>
-  <si>
-    <t>To natural gas
-fraction</t>
-  </si>
-  <si>
-    <t>To hydrogen
-fraction</t>
-  </si>
-  <si>
-    <t>Row total
-must be 1 for fossil fuels</t>
-  </si>
-  <si>
-    <t>Electricity</t>
+    <t>From electricity
+(electricity if)</t>
+  </si>
+  <si>
+    <t>From coal
+(hard coal if)</t>
+  </si>
+  <si>
+    <t>From natural gas
+(natural gas if)</t>
+  </si>
+  <si>
+    <t>From biomass / alternative fuels
+(biomass if)</t>
+  </si>
+  <si>
+    <t>From petroleum diesel
+(petroleum diesel if)</t>
+  </si>
+  <si>
+    <t>From heat
+(heat if)</t>
+  </si>
+  <si>
+    <t>From crude oil
+(crude oil if)</t>
+  </si>
+  <si>
+    <t>From residual fuel oil
+(heavy or residual fuel oil if)</t>
+  </si>
+  <si>
+    <t>From lpg
+(LPG propane or butane if)</t>
+  </si>
+  <si>
+    <t>From hydrogen
+(hydrogen if)</t>
+  </si>
+  <si>
+    <t>From green hydrogen
+(green hydrogen if)</t>
+  </si>
+  <si>
+    <t>From low carbon hydrogen
+(low carbon hydrogen if)</t>
+  </si>
+  <si>
+    <t>Fossil kiln fuel? (1 = yes)</t>
+  </si>
+  <si>
+    <t>To electricity</t>
   </si>
   <si>
     <t>electricity if</t>
   </si>
   <si>
-    <t>Coal</t>
+    <t>To coal</t>
   </si>
   <si>
     <t>hard coal if</t>
   </si>
   <si>
-    <t>Natural gas</t>
+    <t>To natural gas</t>
   </si>
   <si>
     <t>natural gas if</t>
   </si>
   <si>
-    <t>Biomass (carries the alternative fuels)</t>
+    <t>To biomass / alternative fuels</t>
   </si>
   <si>
     <t>biomass if</t>
   </si>
   <si>
-    <t>Petroleum diesel (carries part of the petroleum coke)</t>
+    <t>To petroleum diesel</t>
   </si>
   <si>
     <t>petroleum diesel if</t>
   </si>
   <si>
-    <t>Heat</t>
+    <t>To heat</t>
   </si>
   <si>
     <t>heat if</t>
   </si>
   <si>
-    <t>Crude oil</t>
+    <t>To crude oil</t>
   </si>
   <si>
     <t>crude oil if</t>
   </si>
   <si>
-    <t>Heavy or residual fuel oil (carries part of the petroleum coke)</t>
+    <t>To residual fuel oil</t>
   </si>
   <si>
     <t>heavy or residual fuel oil if</t>
   </si>
   <si>
-    <t>LPG, propane or butane</t>
+    <t>To lpg</t>
   </si>
   <si>
     <t>LPG propane or butane if</t>
   </si>
   <si>
-    <t>Hydrogen</t>
+    <t>To hydrogen</t>
   </si>
   <si>
     <t>hydrogen if</t>
   </si>
   <si>
-    <t>Green hydrogen</t>
+    <t>To green hydrogen</t>
   </si>
   <si>
     <t>green hydrogen if</t>
   </si>
   <si>
-    <t>Low carbon hydrogen</t>
+    <t>To low carbon hydrogen</t>
   </si>
   <si>
     <t>low carbon hydrogen if</t>
   </si>
   <si>
+    <t>Column total (must be 1 for fossil fuels)</t>
+  </si>
+  <si>
     <t>Live checks</t>
   </si>
   <si>
@@ -217,25 +251,16 @@
     <t>Result</t>
   </si>
   <si>
-    <t>Fossil fuel rows whose fractions do not add up to 1 (count)</t>
+    <t>Fossil fuel columns whose fractions do not add up to 1 (count)</t>
   </si>
   <si>
     <t>Fractions below 0 or above 1 (count)</t>
   </si>
   <si>
-    <t>Non-fossil rows with any nonzero fraction (count; these rows are not used)</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless</t>
-  </si>
-  <si>
-    <t>to alternative fuels</t>
-  </si>
-  <si>
-    <t>to natural gas</t>
-  </si>
-  <si>
-    <t>to hydrogen</t>
+    <t>Non-fossil columns with any nonzero fraction (count; these columns are not used)</t>
+  </si>
+  <si>
+    <t>To type (below)  / From type (right)</t>
   </si>
 </sst>
 </file>
@@ -704,7 +729,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>13</v>
       </c>
@@ -747,22 +772,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>22</v>
       </c>
@@ -772,8 +795,15 @@
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
       <c r="G2" s="8"/>
-    </row>
-    <row r="3" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="8"/>
+      <c r="N2" s="8"/>
+    </row>
+    <row r="3" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>23</v>
       </c>
@@ -795,298 +825,653 @@
       <c r="G3" s="6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="H3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="s">
+      <c r="I3" s="6" t="s">
         <v>31</v>
       </c>
+      <c r="J3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G15" si="0">SUM(D4:F4)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="D5">
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17">
+        <f t="shared" ref="C17:N17" si="0">SUM(C5:C16)</f>
+        <v>0</v>
+      </c>
+      <c r="D17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
+      <c r="E17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
+      <c r="F17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
+      <c r="G17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
+      <c r="H17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
+      <c r="I17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
+      <c r="J17">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
+      <c r="K17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
+      <c r="L17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
+      <c r="M17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
+      <c r="N17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A2:N2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1098,31 +1483,30 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70" customWidth="1"/>
-    <col min="2" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="B3">
-        <f>SUMPRODUCT(('Recipient Fractions'!C4:C15=1)*(ABS('Recipient Fractions'!G4:G15-1)&gt;0.000001))</f>
+        <f>SUMPRODUCT(('Recipient Fractions'!C4:N4=1)*(ABS('Recipient Fractions'!C17:N17-1)&gt;0.000001))</f>
         <v>0</v>
       </c>
       <c r="C3" t="str">
@@ -1132,10 +1516,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="B4">
-        <f>COUNTIF('Recipient Fractions'!D4:F15,"&lt;0")+COUNTIF('Recipient Fractions'!D4:F15,"&gt;1")</f>
+        <f>COUNTIF('Recipient Fractions'!C5:N16,"&lt;0")+COUNTIF('Recipient Fractions'!C5:N16,"&gt;1")</f>
         <v>0</v>
       </c>
       <c r="C4" t="str">
@@ -1145,10 +1529,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B5">
-        <f>SUMPRODUCT(('Recipient Fractions'!C4:C15=0)*('Recipient Fractions'!G4:G15&lt;&gt;0))</f>
+        <f>SUMPRODUCT(('Recipient Fractions'!C4:N4=0)*('Recipient Fractions'!C17:N17&lt;&gt;0))</f>
         <v>0</v>
       </c>
       <c r="C5" t="str">
@@ -1166,239 +1550,698 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" t="s">
+        <v>57</v>
+      </c>
+      <c r="L1" t="s">
+        <v>59</v>
+      </c>
+      <c r="M1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f>'Recipient Fractions'!B4</f>
+        <f>'Recipient Fractions'!B5</f>
         <v>electricity if</v>
       </c>
       <c r="B2">
-        <f>'Recipient Fractions'!D4</f>
+        <f>'Recipient Fractions'!C5</f>
         <v>0</v>
       </c>
       <c r="C2">
-        <f>'Recipient Fractions'!E4</f>
+        <f>'Recipient Fractions'!D5</f>
         <v>0</v>
       </c>
       <c r="D2">
-        <f>'Recipient Fractions'!F4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>'Recipient Fractions'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>'Recipient Fractions'!G5</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>'Recipient Fractions'!H5</f>
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <f>'Recipient Fractions'!I5</f>
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <f>'Recipient Fractions'!J5</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>'Recipient Fractions'!K5</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>'Recipient Fractions'!L5</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>'Recipient Fractions'!M5</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>'Recipient Fractions'!N5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <f>'Recipient Fractions'!B5</f>
+        <f>'Recipient Fractions'!B6</f>
         <v>hard coal if</v>
       </c>
       <c r="B3">
-        <f>'Recipient Fractions'!D5</f>
-        <v>1</v>
+        <f>'Recipient Fractions'!C6</f>
+        <v>0</v>
       </c>
       <c r="C3">
-        <f>'Recipient Fractions'!E5</f>
+        <f>'Recipient Fractions'!D6</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f>'Recipient Fractions'!F5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>'Recipient Fractions'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>'Recipient Fractions'!G6</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>'Recipient Fractions'!H6</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>'Recipient Fractions'!I6</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>'Recipient Fractions'!J6</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>'Recipient Fractions'!K6</f>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f>'Recipient Fractions'!L6</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>'Recipient Fractions'!M6</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>'Recipient Fractions'!N6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <f>'Recipient Fractions'!B6</f>
+        <f>'Recipient Fractions'!B7</f>
         <v>natural gas if</v>
       </c>
       <c r="B4">
-        <f>'Recipient Fractions'!D6</f>
-        <v>1</v>
+        <f>'Recipient Fractions'!C7</f>
+        <v>0</v>
       </c>
       <c r="C4">
-        <f>'Recipient Fractions'!E6</f>
+        <f>'Recipient Fractions'!D7</f>
         <v>0</v>
       </c>
       <c r="D4">
-        <f>'Recipient Fractions'!F6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>'Recipient Fractions'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <f>'Recipient Fractions'!G7</f>
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <f>'Recipient Fractions'!H7</f>
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <f>'Recipient Fractions'!I7</f>
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <f>'Recipient Fractions'!J7</f>
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <f>'Recipient Fractions'!K7</f>
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <f>'Recipient Fractions'!L7</f>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f>'Recipient Fractions'!M7</f>
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <f>'Recipient Fractions'!N7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <f>'Recipient Fractions'!B7</f>
+        <f>'Recipient Fractions'!B8</f>
         <v>biomass if</v>
       </c>
       <c r="B5">
-        <f>'Recipient Fractions'!D7</f>
+        <f>'Recipient Fractions'!C8</f>
         <v>0</v>
       </c>
       <c r="C5">
-        <f>'Recipient Fractions'!E7</f>
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <f>'Recipient Fractions'!F7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="str">
-        <f>'Recipient Fractions'!B8</f>
-        <v>petroleum diesel if</v>
-      </c>
-      <c r="B6">
         <f>'Recipient Fractions'!D8</f>
         <v>1</v>
       </c>
+      <c r="D5">
+        <f>'Recipient Fractions'!E8</f>
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <f>'Recipient Fractions'!F8</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>'Recipient Fractions'!G8</f>
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <f>'Recipient Fractions'!H8</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>'Recipient Fractions'!I8</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f>'Recipient Fractions'!J8</f>
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <f>'Recipient Fractions'!K8</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>'Recipient Fractions'!L8</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f>'Recipient Fractions'!M8</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f>'Recipient Fractions'!N8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <f>'Recipient Fractions'!B9</f>
+        <v>petroleum diesel if</v>
+      </c>
+      <c r="B6">
+        <f>'Recipient Fractions'!C9</f>
+        <v>0</v>
+      </c>
       <c r="C6">
-        <f>'Recipient Fractions'!E8</f>
+        <f>'Recipient Fractions'!D9</f>
         <v>0</v>
       </c>
       <c r="D6">
-        <f>'Recipient Fractions'!F8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f>'Recipient Fractions'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>'Recipient Fractions'!G9</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f>'Recipient Fractions'!H9</f>
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <f>'Recipient Fractions'!I9</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>'Recipient Fractions'!J9</f>
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <f>'Recipient Fractions'!K9</f>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f>'Recipient Fractions'!L9</f>
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <f>'Recipient Fractions'!M9</f>
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <f>'Recipient Fractions'!N9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <f>'Recipient Fractions'!B9</f>
+        <f>'Recipient Fractions'!B10</f>
         <v>heat if</v>
       </c>
       <c r="B7">
-        <f>'Recipient Fractions'!D9</f>
+        <f>'Recipient Fractions'!C10</f>
         <v>0</v>
       </c>
       <c r="C7">
-        <f>'Recipient Fractions'!E9</f>
+        <f>'Recipient Fractions'!D10</f>
         <v>0</v>
       </c>
       <c r="D7">
-        <f>'Recipient Fractions'!F9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>'Recipient Fractions'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>'Recipient Fractions'!G10</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f>'Recipient Fractions'!H10</f>
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <f>'Recipient Fractions'!I10</f>
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <f>'Recipient Fractions'!J10</f>
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <f>'Recipient Fractions'!K10</f>
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <f>'Recipient Fractions'!L10</f>
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <f>'Recipient Fractions'!M10</f>
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <f>'Recipient Fractions'!N10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <f>'Recipient Fractions'!B10</f>
+        <f>'Recipient Fractions'!B11</f>
         <v>crude oil if</v>
       </c>
       <c r="B8">
-        <f>'Recipient Fractions'!D10</f>
+        <f>'Recipient Fractions'!C11</f>
         <v>0</v>
       </c>
       <c r="C8">
-        <f>'Recipient Fractions'!E10</f>
+        <f>'Recipient Fractions'!D11</f>
         <v>0</v>
       </c>
       <c r="D8">
-        <f>'Recipient Fractions'!F10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <f>'Recipient Fractions'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f>'Recipient Fractions'!G11</f>
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <f>'Recipient Fractions'!H11</f>
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <f>'Recipient Fractions'!I11</f>
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <f>'Recipient Fractions'!J11</f>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <f>'Recipient Fractions'!K11</f>
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <f>'Recipient Fractions'!L11</f>
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <f>'Recipient Fractions'!M11</f>
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <f>'Recipient Fractions'!N11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <f>'Recipient Fractions'!B11</f>
+        <f>'Recipient Fractions'!B12</f>
         <v>heavy or residual fuel oil if</v>
       </c>
       <c r="B9">
-        <f>'Recipient Fractions'!D11</f>
-        <v>1</v>
+        <f>'Recipient Fractions'!C12</f>
+        <v>0</v>
       </c>
       <c r="C9">
-        <f>'Recipient Fractions'!E11</f>
+        <f>'Recipient Fractions'!D12</f>
         <v>0</v>
       </c>
       <c r="D9">
-        <f>'Recipient Fractions'!F11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f>'Recipient Fractions'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f>'Recipient Fractions'!G12</f>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f>'Recipient Fractions'!H12</f>
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <f>'Recipient Fractions'!I12</f>
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <f>'Recipient Fractions'!J12</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f>'Recipient Fractions'!K12</f>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f>'Recipient Fractions'!L12</f>
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <f>'Recipient Fractions'!M12</f>
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <f>'Recipient Fractions'!N12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
-        <f>'Recipient Fractions'!B12</f>
+        <f>'Recipient Fractions'!B13</f>
         <v>LPG propane or butane if</v>
       </c>
       <c r="B10">
-        <f>'Recipient Fractions'!D12</f>
+        <f>'Recipient Fractions'!C13</f>
         <v>0</v>
       </c>
       <c r="C10">
-        <f>'Recipient Fractions'!E12</f>
+        <f>'Recipient Fractions'!D13</f>
         <v>0</v>
       </c>
       <c r="D10">
-        <f>'Recipient Fractions'!F12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E13</f>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f>'Recipient Fractions'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f>'Recipient Fractions'!G13</f>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f>'Recipient Fractions'!H13</f>
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <f>'Recipient Fractions'!I13</f>
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <f>'Recipient Fractions'!J13</f>
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f>'Recipient Fractions'!K13</f>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f>'Recipient Fractions'!L13</f>
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <f>'Recipient Fractions'!M13</f>
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <f>'Recipient Fractions'!N13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
-        <f>'Recipient Fractions'!B13</f>
+        <f>'Recipient Fractions'!B14</f>
         <v>hydrogen if</v>
       </c>
       <c r="B11">
-        <f>'Recipient Fractions'!D13</f>
+        <f>'Recipient Fractions'!C14</f>
         <v>0</v>
       </c>
       <c r="C11">
-        <f>'Recipient Fractions'!E13</f>
+        <f>'Recipient Fractions'!D14</f>
         <v>0</v>
       </c>
       <c r="D11">
-        <f>'Recipient Fractions'!F13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f>'Recipient Fractions'!F14</f>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f>'Recipient Fractions'!G14</f>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <f>'Recipient Fractions'!H14</f>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f>'Recipient Fractions'!I14</f>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f>'Recipient Fractions'!J14</f>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f>'Recipient Fractions'!K14</f>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f>'Recipient Fractions'!L14</f>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f>'Recipient Fractions'!M14</f>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f>'Recipient Fractions'!N14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
-        <f>'Recipient Fractions'!B14</f>
+        <f>'Recipient Fractions'!B15</f>
         <v>green hydrogen if</v>
       </c>
       <c r="B12">
-        <f>'Recipient Fractions'!D14</f>
+        <f>'Recipient Fractions'!C15</f>
         <v>0</v>
       </c>
       <c r="C12">
-        <f>'Recipient Fractions'!E14</f>
+        <f>'Recipient Fractions'!D15</f>
         <v>0</v>
       </c>
       <c r="D12">
-        <f>'Recipient Fractions'!F14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+        <f>'Recipient Fractions'!E15</f>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f>'Recipient Fractions'!F15</f>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f>'Recipient Fractions'!G15</f>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f>'Recipient Fractions'!H15</f>
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <f>'Recipient Fractions'!I15</f>
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <f>'Recipient Fractions'!J15</f>
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <f>'Recipient Fractions'!K15</f>
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <f>'Recipient Fractions'!L15</f>
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <f>'Recipient Fractions'!M15</f>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <f>'Recipient Fractions'!N15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
-        <f>'Recipient Fractions'!B15</f>
+        <f>'Recipient Fractions'!B16</f>
         <v>low carbon hydrogen if</v>
       </c>
       <c r="B13">
-        <f>'Recipient Fractions'!D15</f>
+        <f>'Recipient Fractions'!C16</f>
         <v>0</v>
       </c>
       <c r="C13">
-        <f>'Recipient Fractions'!E15</f>
+        <f>'Recipient Fractions'!D16</f>
         <v>0</v>
       </c>
       <c r="D13">
-        <f>'Recipient Fractions'!F15</f>
+        <f>'Recipient Fractions'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f>'Recipient Fractions'!F16</f>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>'Recipient Fractions'!G16</f>
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f>'Recipient Fractions'!H16</f>
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <f>'Recipient Fractions'!I16</f>
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <f>'Recipient Fractions'!J16</f>
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f>'Recipient Fractions'!K16</f>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f>'Recipient Fractions'!L16</f>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <f>'Recipient Fractions'!M16</f>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f>'Recipient Fractions'!N16</f>
         <v>0</v>
       </c>
     </row>

--- a/InputData/indst/_cement/CKFSR/Cement Kiln Fuel Shift Recipient Fractions.xlsx
+++ b/InputData/indst/_cement/CKFSR/Cement Kiln Fuel Shift Recipient Fractions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\CKFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{289B923F-A657-4032-A755-C2461ECA3618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3825DE0A-4918-4078-ADEF-86FA53FAF74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
   <si>
     <t>CKFSR Cement Kiln Fuel Shift Recipient Fractions</t>
   </si>
@@ -153,14 +153,6 @@
 (hydrogen if)</t>
   </si>
   <si>
-    <t>From green hydrogen
-(green hydrogen if)</t>
-  </si>
-  <si>
-    <t>From low carbon hydrogen
-(low carbon hydrogen if)</t>
-  </si>
-  <si>
     <t>Fossil kiln fuel? (1 = yes)</t>
   </si>
   <si>
@@ -222,18 +214,6 @@
   </si>
   <si>
     <t>hydrogen if</t>
-  </si>
-  <si>
-    <t>To green hydrogen</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>To low carbon hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
   <si>
     <t>Column total (must be 1 for fossil fuels)</t>
@@ -772,20 +752,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="14" width="14" customWidth="1"/>
+    <col min="3" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>22</v>
       </c>
@@ -800,10 +780,8 @@
       <c r="J2" s="8"/>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3" spans="1:14" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:12" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>23</v>
       </c>
@@ -840,16 +818,10 @@
       <c r="L3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="6" t="s">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -881,151 +853,127 @@
       <c r="L4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>38</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>39</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>40</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>41</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>42</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>43</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" t="s">
-        <v>45</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1057,421 +1005,283 @@
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>46</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>47</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>48</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>49</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>50</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>51</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>52</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>53</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>54</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>55</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
       <c r="C15">
+        <f>SUM(C5:C14)</f>
         <v>0</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <f>SUM(D5:D14)</f>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <f>SUM(E5:E14)</f>
+        <v>1</v>
       </c>
       <c r="F15">
+        <f>SUM(F5:F14)</f>
         <v>0</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <f>SUM(G5:G14)</f>
+        <v>1</v>
       </c>
       <c r="H15">
+        <f>SUM(H5:H14)</f>
         <v>0</v>
       </c>
       <c r="I15">
+        <f>SUM(I5:I14)</f>
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <f>SUM(J5:J14)</f>
+        <v>1</v>
       </c>
       <c r="K15">
+        <f>SUM(K5:K14)</f>
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17">
-        <f t="shared" ref="C17:N17" si="0">SUM(C5:C16)</f>
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <f t="shared" si="0"/>
+        <f>SUM(L5:L14)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1487,26 +1297,26 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B3">
-        <f>SUMPRODUCT(('Recipient Fractions'!C4:N4=1)*(ABS('Recipient Fractions'!C17:N17-1)&gt;0.000001))</f>
+        <f>SUMPRODUCT(('Recipient Fractions'!C4:L4=1)*(ABS('Recipient Fractions'!C15:L15-1)&gt;0.000001))</f>
         <v>0</v>
       </c>
       <c r="C3" t="str">
@@ -1516,10 +1326,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B4">
-        <f>COUNTIF('Recipient Fractions'!C5:N16,"&lt;0")+COUNTIF('Recipient Fractions'!C5:N16,"&gt;1")</f>
+        <f>COUNTIF('Recipient Fractions'!C5:L14,"&lt;0")+COUNTIF('Recipient Fractions'!C5:L14,"&gt;1")</f>
         <v>0</v>
       </c>
       <c r="C4" t="str">
@@ -1529,10 +1339,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B5">
-        <f>SUMPRODUCT(('Recipient Fractions'!C4:N4=0)*('Recipient Fractions'!C17:N17&lt;&gt;0))</f>
+        <f>SUMPRODUCT(('Recipient Fractions'!C4:L4=0)*('Recipient Fractions'!C15:L15&lt;&gt;0))</f>
         <v>0</v>
       </c>
       <c r="C5" t="str">
@@ -1550,54 +1360,48 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" t="s">
         <v>39</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>45</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>47</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>49</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>51</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>53</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>55</v>
       </c>
-      <c r="K1" t="s">
-        <v>57</v>
-      </c>
-      <c r="L1" t="s">
-        <v>59</v>
-      </c>
-      <c r="M1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
         <f>'Recipient Fractions'!B5</f>
         <v>electricity if</v>
@@ -1642,16 +1446,8 @@
         <f>'Recipient Fractions'!L5</f>
         <v>0</v>
       </c>
-      <c r="L2">
-        <f>'Recipient Fractions'!M5</f>
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <f>'Recipient Fractions'!N5</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
         <f>'Recipient Fractions'!B6</f>
         <v>hard coal if</v>
@@ -1696,16 +1492,8 @@
         <f>'Recipient Fractions'!L6</f>
         <v>0</v>
       </c>
-      <c r="L3">
-        <f>'Recipient Fractions'!M6</f>
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <f>'Recipient Fractions'!N6</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>'Recipient Fractions'!B7</f>
         <v>natural gas if</v>
@@ -1750,16 +1538,8 @@
         <f>'Recipient Fractions'!L7</f>
         <v>0</v>
       </c>
-      <c r="L4">
-        <f>'Recipient Fractions'!M7</f>
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <f>'Recipient Fractions'!N7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>'Recipient Fractions'!B8</f>
         <v>biomass if</v>
@@ -1804,16 +1584,8 @@
         <f>'Recipient Fractions'!L8</f>
         <v>0</v>
       </c>
-      <c r="L5">
-        <f>'Recipient Fractions'!M8</f>
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <f>'Recipient Fractions'!N8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
         <f>'Recipient Fractions'!B9</f>
         <v>petroleum diesel if</v>
@@ -1858,16 +1630,8 @@
         <f>'Recipient Fractions'!L9</f>
         <v>0</v>
       </c>
-      <c r="L6">
-        <f>'Recipient Fractions'!M9</f>
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <f>'Recipient Fractions'!N9</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
         <f>'Recipient Fractions'!B10</f>
         <v>heat if</v>
@@ -1912,16 +1676,8 @@
         <f>'Recipient Fractions'!L10</f>
         <v>0</v>
       </c>
-      <c r="L7">
-        <f>'Recipient Fractions'!M10</f>
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <f>'Recipient Fractions'!N10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
         <f>'Recipient Fractions'!B11</f>
         <v>crude oil if</v>
@@ -1966,16 +1722,8 @@
         <f>'Recipient Fractions'!L11</f>
         <v>0</v>
       </c>
-      <c r="L8">
-        <f>'Recipient Fractions'!M11</f>
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <f>'Recipient Fractions'!N11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
         <f>'Recipient Fractions'!B12</f>
         <v>heavy or residual fuel oil if</v>
@@ -2020,16 +1768,8 @@
         <f>'Recipient Fractions'!L12</f>
         <v>0</v>
       </c>
-      <c r="L9">
-        <f>'Recipient Fractions'!M12</f>
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <f>'Recipient Fractions'!N12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
         <f>'Recipient Fractions'!B13</f>
         <v>LPG propane or butane if</v>
@@ -2074,16 +1814,8 @@
         <f>'Recipient Fractions'!L13</f>
         <v>0</v>
       </c>
-      <c r="L10">
-        <f>'Recipient Fractions'!M13</f>
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <f>'Recipient Fractions'!N13</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
         <f>'Recipient Fractions'!B14</f>
         <v>hydrogen if</v>
@@ -2126,122 +1858,6 @@
       </c>
       <c r="K11">
         <f>'Recipient Fractions'!L14</f>
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <f>'Recipient Fractions'!M14</f>
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <f>'Recipient Fractions'!N14</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" t="str">
-        <f>'Recipient Fractions'!B15</f>
-        <v>green hydrogen if</v>
-      </c>
-      <c r="B12">
-        <f>'Recipient Fractions'!C15</f>
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <f>'Recipient Fractions'!D15</f>
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <f>'Recipient Fractions'!E15</f>
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <f>'Recipient Fractions'!F15</f>
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <f>'Recipient Fractions'!G15</f>
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <f>'Recipient Fractions'!H15</f>
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <f>'Recipient Fractions'!I15</f>
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <f>'Recipient Fractions'!J15</f>
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <f>'Recipient Fractions'!K15</f>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>'Recipient Fractions'!L15</f>
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <f>'Recipient Fractions'!M15</f>
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <f>'Recipient Fractions'!N15</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" t="str">
-        <f>'Recipient Fractions'!B16</f>
-        <v>low carbon hydrogen if</v>
-      </c>
-      <c r="B13">
-        <f>'Recipient Fractions'!C16</f>
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <f>'Recipient Fractions'!D16</f>
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <f>'Recipient Fractions'!E16</f>
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <f>'Recipient Fractions'!F16</f>
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <f>'Recipient Fractions'!G16</f>
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <f>'Recipient Fractions'!H16</f>
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <f>'Recipient Fractions'!I16</f>
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <f>'Recipient Fractions'!J16</f>
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <f>'Recipient Fractions'!K16</f>
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f>'Recipient Fractions'!L16</f>
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <f>'Recipient Fractions'!M16</f>
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <f>'Recipient Fractions'!N16</f>
         <v>0</v>
       </c>
     </row>
